--- a/Gestion Stock 2025/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2025.xlsx
+++ b/Gestion Stock 2025/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2025.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2025\Gestion de Stock Tlathet Douairs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE40A73-E4DC-4546-9396-D6A777704C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8A8A06-12A3-4464-BC84-8C3C1CEF05BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="JANVIER 2024" sheetId="12" r:id="rId1"/>
+    <sheet name="JANVIER 2025" sheetId="12" r:id="rId1"/>
     <sheet name="FEVRIER 2025" sheetId="13" r:id="rId2"/>
     <sheet name="MARS 2025" sheetId="14" r:id="rId3"/>
     <sheet name="AVRIL 2025" sheetId="15" r:id="rId4"/>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'AVRIL 2025'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'DECEMBRE 2025'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'FEVRIER 2025'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'JANVIER 2024'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'JANVIER 2025'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'JUILLET 2025'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'JUIN 2025'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MAI 2025'!$1:$6</definedName>

--- a/Gestion Stock 2025/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2025.xlsx
+++ b/Gestion Stock 2025/Gestion de Stock Tlathet Douairs/Suivie pose Compteur Tlathet Douairs 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Suivie Pose Compteurs\Gestion Stock 2025\Gestion de Stock Tlathet Douairs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8A8A06-12A3-4464-BC84-8C3C1CEF05BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2C9B8D-B7AB-4BF9-96C7-4E576C7F168A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JANVIER 2025" sheetId="12" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="692">
   <si>
     <t>Algérienne des Eaux</t>
   </si>
@@ -2381,6 +2381,9 @@
   </si>
   <si>
     <t>11/12/2025</t>
+  </si>
+  <si>
+    <t>641619</t>
   </si>
 </sst>
 </file>
@@ -24338,12 +24341,12 @@
         <v>11</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>21</v>
+        <v>691</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="21" t="s">
         <v>155</v>
       </c>
       <c r="E17" s="9" t="s">
